--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 13,08,26 лгрсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 13,08,26 лгрсч пок зпф.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB02E611-AA1E-48F3-8AA9-FF9AEFBBC227}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACB8E19-080D-4E65-9B43-D57FABD97445}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AL$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AL$72</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -566,7 +566,7 @@
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,8 +600,16 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -633,6 +641,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,7 +686,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -697,6 +711,7 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -8907,7 +8922,7 @@
       <c r="AD61" s="5">
         <v>11.8</v>
       </c>
-      <c r="AE61" s="5" t="s">
+      <c r="AE61" s="24" t="s">
         <v>110</v>
       </c>
       <c r="AF61" s="5">
@@ -31234,8 +31249,8 @@
       <c r="AU499" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AL70" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AL72" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>